--- a/outputs/EISPOT_0V_3_#1.xlsx
+++ b/outputs/EISPOT_0V_3_#1.xlsx
@@ -423,29 +423,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Campo</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unidad</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Técnica</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -453,11 +459,12 @@
           <t>Potentiostatic EIS</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -465,11 +472,12 @@
           <t>24/2/2026</t>
         </is>
       </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Hora</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -477,6 +485,7 @@
           <t>4:26:16</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -487,55 +496,85 @@
       <c r="B5" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>freqinit</t>
+          <t>Frecuencia inicial</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>100000</v>
       </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>freqfinal</t>
+          <t>Frecuencia final</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1000</v>
       </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ptsperdec</t>
+          <t>Puntos por década</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>points/decade</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>vac</t>
+          <t>Amplitud</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>mV rms</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>Área</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>25</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>cm^2</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -549,11 +588,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -572,7 +611,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Frecuencia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -612,679 +651,727 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Temperatura</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>100078.1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.0137323</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.0059792</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.0149775</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>23.52899</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>-0.0002215</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1.387381</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>63.58242</v>
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ohm</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ohm</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ohm</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>79453.13</v>
+        <v>100078.1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.0136055</v>
+        <v>0.0137323</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.0048294</v>
+        <v>0.0059792</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.0144372</v>
+        <v>0.0149775</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>19.54267</v>
+        <v>23.52899</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-0.0006671</v>
+        <v>-0.0002215</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.387365</v>
+        <v>1.387381</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>63.57964</v>
+        <v>63.58242</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>63140.62</v>
+        <v>79453.13</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.0135029</v>
+        <v>0.0136055</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0039031</v>
+        <v>0.0048294</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0140557</v>
+        <v>0.0144372</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>16.12242</v>
+        <v>19.54267</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.0003172</v>
+        <v>-0.0006671</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.387391</v>
+        <v>1.387365</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>63.56591</v>
+        <v>63.57964</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>50203.12</v>
+        <v>63140.62</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.0134188</v>
+        <v>0.0135029</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0031506</v>
+        <v>0.0039031</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.0137837</v>
+        <v>0.0140557</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13.21299</v>
+        <v>16.12242</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.0004966</v>
+        <v>0.0003172</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.387377</v>
+        <v>1.387391</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63.55762</v>
+        <v>63.56591</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>39890.62</v>
+        <v>50203.12</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.0133486</v>
+        <v>0.0134188</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.0025343</v>
+        <v>0.0031506</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.013587</v>
+        <v>0.0137837</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>10.74985</v>
+        <v>13.21299</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.0007608</v>
+        <v>0.0004966</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.387373</v>
+        <v>1.387377</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>63.54157</v>
+        <v>63.55762</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>31640.63</v>
+        <v>39890.62</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.013296</v>
+        <v>0.0133486</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.0020266</v>
+        <v>0.0025343</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.0134496</v>
+        <v>0.013587</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>8.666458</v>
+        <v>10.74985</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0003791</v>
+        <v>0.0007608</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1.387369</v>
+        <v>1.387373</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>63.53668</v>
+        <v>63.54157</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>25171.88</v>
+        <v>31640.63</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.013263</v>
+        <v>0.013296</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.001617</v>
+        <v>0.0020266</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.0133613</v>
+        <v>0.0134496</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>6.95121</v>
+        <v>8.666458</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.0013366</v>
+        <v>0.0003791</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1.387375</v>
+        <v>1.387369</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>63.52956</v>
+        <v>63.53668</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>20015.62</v>
+        <v>25171.88</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.013234</v>
+        <v>0.013263</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.0012854</v>
+        <v>0.001617</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.0132962</v>
+        <v>0.0133613</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>5.547637</v>
+        <v>6.95121</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.0015274</v>
+        <v>0.0013366</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>1.387375</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>63.52074</v>
+        <v>63.52956</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>15890.62</v>
+        <v>20015.62</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.0132163</v>
+        <v>0.013234</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.0010099</v>
+        <v>0.0012854</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.0132548</v>
+        <v>0.0132962</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.369631</v>
+        <v>5.547637</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.001944</v>
+        <v>0.0015274</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1.387355</v>
+        <v>1.387375</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>63.51211</v>
+        <v>63.52074</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12609.38</v>
+        <v>15890.62</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.0132045</v>
+        <v>0.0132163</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.0007865</v>
+        <v>0.0010099</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.0132279</v>
+        <v>0.0132548</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3.408882</v>
+        <v>4.369631</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.0014973</v>
+        <v>0.001944</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1.38738</v>
+        <v>1.387355</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>63.52031</v>
+        <v>63.51211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10078.13</v>
+        <v>12609.38</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.013202</v>
+        <v>0.0132045</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.0006019</v>
+        <v>0.0007865</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.0132157</v>
+        <v>0.0132279</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2.610275</v>
+        <v>3.408882</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.0020999</v>
+        <v>0.0014973</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1.387371</v>
+        <v>1.38738</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>63.50771</v>
+        <v>63.52031</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>8015.625</v>
+        <v>10078.13</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.0132007</v>
+        <v>0.013202</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.0004476</v>
+        <v>0.0006019</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.0132083</v>
+        <v>0.0132157</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1.941786</v>
+        <v>2.610275</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.0017894</v>
+        <v>0.0020999</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.38737</v>
+        <v>1.387371</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>63.50611</v>
+        <v>63.50771</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>6328.125</v>
+        <v>8015.625</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.0132031</v>
+        <v>0.0132007</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.0003121</v>
+        <v>0.0004476</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.0132068</v>
+        <v>0.0132083</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.353923</v>
+        <v>1.941786</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.001863</v>
+        <v>0.0017894</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.38738</v>
+        <v>1.38737</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>63.49555</v>
+        <v>63.50611</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>5015.625</v>
+        <v>6328.125</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.0132057</v>
+        <v>0.0132031</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.0001956</v>
+        <v>0.0003121</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.0132072</v>
+        <v>0.0132068</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.8487722</v>
+        <v>1.353923</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.0021261</v>
+        <v>0.001863</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.387368</v>
+        <v>1.38738</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>63.49653</v>
+        <v>63.49555</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3984.375</v>
+        <v>5015.625</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.0132158</v>
+        <v>0.0132057</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9.235365999999999e-05</v>
+        <v>0.0001956</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.0132161</v>
+        <v>0.0132072</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.4003843</v>
+        <v>0.8487722</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.002344</v>
+        <v>0.0021261</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.387372</v>
+        <v>1.387368</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>63.48764</v>
+        <v>63.49653</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3170.956</v>
+        <v>3984.375</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.0132295</v>
+        <v>0.0132158</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-2.341682e-06</v>
+        <v>9.235365999999999e-05</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.0132295</v>
+        <v>0.0132161</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.0101416</v>
+        <v>0.4003843</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.002906</v>
+        <v>0.002344</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.38738</v>
+        <v>1.387372</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>63.48249</v>
+        <v>63.48764</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2527.573</v>
+        <v>3170.956</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.0132475</v>
+        <v>0.0132295</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-9.341346e-05</v>
+        <v>-2.341682e-06</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.0132479</v>
+        <v>0.0132295</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.4040082</v>
+        <v>-0.0101416</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.0026397</v>
+        <v>0.002906</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.387393</v>
+        <v>1.38738</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>63.48103</v>
+        <v>63.48249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1976.103</v>
+        <v>2527.573</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.0132741</v>
+        <v>0.0132475</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-0.0001867</v>
+        <v>-9.341346e-05</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.0132754</v>
+        <v>0.0132479</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.8057763</v>
+        <v>-0.4040082</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.0023548</v>
+        <v>0.0026397</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.387369</v>
+        <v>1.387393</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>63.47601</v>
+        <v>63.48103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1577.524</v>
+        <v>1976.103</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0132741</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-0.0002797</v>
+        <v>-0.0001867</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.013303</v>
+        <v>0.0132754</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-1.204731</v>
+        <v>-0.8057763</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.0031261</v>
+        <v>0.0023548</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1.387363</v>
+        <v>1.387369</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>63.46599</v>
+        <v>63.47601</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1265.625</v>
+        <v>1577.524</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.0133336</v>
+        <v>0.0133</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-0.0003722</v>
+        <v>-0.0002797</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.0133388</v>
+        <v>0.013303</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-1.598902</v>
+        <v>-1.204731</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.0027387</v>
+        <v>0.0031261</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1.387373</v>
+        <v>1.387363</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>63.45262</v>
+        <v>63.46599</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1265.625</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0.0133336</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>-0.0003722</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.0133388</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>-1.598902</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.0027387</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>1.387373</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>63.45262</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>998.264</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C23" s="2" t="n">
         <v>0.0133704</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D23" s="2" t="n">
         <v>-0.0004775</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="n">
+      <c r="E23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="n">
         <v>0.013379</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>-2.045301</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>0.0026863</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I23" s="2" t="n">
         <v>1.387378</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>63.43359</v>
       </c>
     </row>

--- a/outputs/EISPOT_0V_3_#1.xlsx
+++ b/outputs/EISPOT_0V_3_#1.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>points/decade</t>
+          <t>puntos/década</t>
         </is>
       </c>
     </row>
